--- a/Sample_Statutory_Report_RRK_and_CO_Partnership_Firm.xlsx
+++ b/Sample_Statutory_Report_RRK_and_CO_Partnership_Firm.xlsx
@@ -4705,7 +4705,7 @@
         <v>950000</v>
       </c>
       <c r="D21" s="18">
-        <v>820000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
@@ -4719,7 +4719,7 @@
         <v>2460000</v>
       </c>
       <c r="D22" s="18">
-        <v>2150000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1">
@@ -8438,7 +8438,7 @@
         <v>950000</v>
       </c>
       <c r="F117" s="80">
-        <v>820000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="118" ht="22" customHeight="1">
@@ -8458,7 +8458,7 @@
         <v>2460000</v>
       </c>
       <c r="F118" s="84">
-        <v>2150000</v>
+        <v>2100000</v>
       </c>
     </row>
     <row r="119" ht="22" customHeight="1">
@@ -8498,7 +8498,7 @@
         <v>950000</v>
       </c>
       <c r="F120" s="80">
-        <v>820000</v>
+        <v>800000</v>
       </c>
     </row>
     <row r="121" ht="22" customHeight="1">
@@ -8649,10 +8649,10 @@
         <v>(ii) Others</v>
       </c>
       <c r="C128" s="84">
-        <v>2460000</v>
+        <v>2310000</v>
       </c>
       <c r="D128" s="84">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="E128" s="84">
         <v>0</v>
@@ -8709,10 +8709,10 @@
         <v>Total Trade Payables Aging</v>
       </c>
       <c r="C131" s="21">
-        <v>3410000</v>
+        <v>3260000</v>
       </c>
       <c r="D131" s="21">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="E131" s="21">
         <v>0</v>
